--- a/scenario réaliste/ARC_reel.xlsx
+++ b/scenario réaliste/ARC_reel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\scenario réaliste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D52E857-7012-45EB-942A-2293726BEF79}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250431EF-8948-4782-A455-DE5D269E82B9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="3" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="4" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
   </bookViews>
   <sheets>
     <sheet name="mun" sheetId="3" r:id="rId1"/>
@@ -750,13 +750,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A1C762-7C0F-4506-9633-75512DFB1A94}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -781,8 +781,12 @@
         <f>SUM(B2:C2)</f>
         <v>2944</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G2">
+        <f>B2*0.7*0.5</f>
+        <v>264.41754581528812</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -803,7 +807,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -818,7 +822,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -833,7 +837,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -848,7 +852,7 @@
         <v>130.99999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -863,7 +867,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -878,7 +882,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -893,7 +897,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -908,7 +912,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -923,7 +927,7 @@
         <v>29.999999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -938,7 +942,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -953,7 +957,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -968,7 +972,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -983,7 +987,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -996,6 +1000,10 @@
       <c r="D16">
         <f t="shared" si="0"/>
         <v>42</v>
+      </c>
+      <c r="M16">
+        <f>((254+258+58)*1000*0.15)/36529</f>
+        <v>2.3406060937884967</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1955,8 +1963,17 @@
   <dimension ref="A1:AB28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.81640625" customWidth="1"/>
-    <col min="2" max="11" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.81640625" bestFit="1" customWidth="1"/>
@@ -3261,7 +3278,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B83A381-22AF-46A0-9DDF-5B74B916E2B3}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.7265625" customWidth="1"/>
@@ -3448,6 +3465,12 @@
         <v>11</v>
       </c>
     </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B25">
+        <f>SUM(B2:B23)</f>
+        <v>373.06836916114435</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
